--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T10:23:38+00:00</t>
+    <t>2025-02-24T13:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
@@ -55,13 +55,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>true</t>
+    <t>false</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:55:23+00:00</t>
+    <t>2025-02-26T08:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T08:56:44+00:00</t>
+    <t>2025-03-04T11:06:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T11:06:18+00:00</t>
+    <t>2025-03-06T12:24:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T12:24:43+00:00</t>
+    <t>2025-03-20T12:28:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T12:28:15+00:00</t>
+    <t>2025-03-24T06:28:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-aps-immunization-vaccine-codes</t>
+    <t>https://fhir.hl7.at/elga/aps/r4/ValueSet/at-aps-immunization-vaccine-codes</t>
   </si>
   <si>
     <t>Version</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T06:28:05+00:00</t>
+    <t>2025-03-24T07:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T07:27:46+00:00</t>
+    <t>2025-03-24T07:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T10:23:29+00:00</t>
+    <t>2026-01-28T10:05:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T10:05:57+00:00</t>
+    <t>2026-01-29T06:33:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T06:33:09+00:00</t>
+    <t>2026-02-03T10:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:06:44+00:00</t>
+    <t>2026-02-03T10:34:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/ValueSet-at-aps-immunization-vaccine-codes.xlsx
@@ -43,7 +43,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>AT APS Immunitzation Vaccine Codes</t>
+    <t>AT APS Immunization Vaccine Codes</t>
   </si>
   <si>
     <t>Status</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:34:36+00:00</t>
+    <t>2026-02-09T07:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
